--- a/documentos/modelo_dicionario_de_dados.xlsx
+++ b/documentos/modelo_dicionario_de_dados.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="99">
   <si>
     <t xml:space="preserve">MODELO DE DICIONÁRIO DE DADOS</t>
   </si>
@@ -75,6 +75,54 @@
     <t xml:space="preserve">Descrição / Regra de Negócio</t>
   </si>
   <si>
+    <t xml:space="preserve">funcionario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOINCREMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chave primária de identificação do funcionário.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEXT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo do nome do funcionário.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primária de identificação do cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo do nome do cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">equipamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primária de identificação do equipamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo do nome do equipamento.</t>
+  </si>
+  <si>
     <t xml:space="preserve">INSTRUÇÕES E EXEMPLO PRÁTICO</t>
   </si>
   <si>
@@ -153,18 +201,9 @@
     <t xml:space="preserve">id_aluno</t>
   </si>
   <si>
-    <t xml:space="preserve">INT</t>
-  </si>
-  <si>
     <t xml:space="preserve">11</t>
   </si>
   <si>
-    <t xml:space="preserve">PK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NÃO</t>
-  </si>
-  <si>
     <t xml:space="preserve">AUTO_INCREMENT</t>
   </si>
   <si>
@@ -268,9 +307,6 @@
   </si>
   <si>
     <t xml:space="preserve">VARCHAR(255)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEXT</t>
   </si>
   <si>
     <t xml:space="preserve">DECIMAL(10,2)</t>
@@ -292,7 +328,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -353,6 +389,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <name val="Consolas"/>
       <family val="0"/>
@@ -436,72 +479,80 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -760,632 +811,704 @@
   <dimension ref="A1:I59"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="9"/>
+      <c r="A10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="13"/>
+      <c r="A11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="14" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="9"/>
+      <c r="A12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="10" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="13"/>
+      <c r="A13" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="14" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="9"/>
+      <c r="A14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="10" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="13"/>
+      <c r="A15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="14" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="9"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="13"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="9"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="13"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="9"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="13"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="9"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="13"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="9"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="13"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="9"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="13"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="9"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="13"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="14"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="9"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="13"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="14"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="9"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="13"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="14"/>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="9"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="13"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="14"/>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="9"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="13"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="14"/>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="9"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="13"/>
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="14"/>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="9"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="13"/>
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="14"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="9"/>
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="13"/>
+      <c r="A43" s="11"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="14"/>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="9"/>
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="13"/>
+      <c r="A45" s="11"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="14"/>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="9"/>
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="13"/>
+      <c r="A47" s="11"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="14"/>
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="9"/>
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="10"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="13"/>
+      <c r="A49" s="11"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="14"/>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="9"/>
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="10"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="13"/>
+      <c r="A51" s="11"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="14"/>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="9"/>
+      <c r="A52" s="7"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="10"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="13"/>
+      <c r="A53" s="11"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="14"/>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="9"/>
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="10"/>
-      <c r="B55" s="10"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="13"/>
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="14"/>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="9"/>
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="10"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="10"/>
-      <c r="I57" s="13"/>
+      <c r="A57" s="11"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="14"/>
     </row>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="9"/>
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="10"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="13"/>
+      <c r="A59" s="11"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -1420,373 +1543,373 @@
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>17</v>
+      <c r="A1" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>18</v>
+      <c r="A2" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="D17" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+      <c r="F17" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>49</v>
+      <c r="G17" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>54</v>
+      <c r="A18" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>56</v>
+      <c r="A19" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="6" t="s">
+      <c r="A20" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H20" s="6" t="s">
+      <c r="B20" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="10" t="s">
+      <c r="E22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F21" s="12" t="s">
+      <c r="H23" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="6" t="s">
+      <c r="I23" s="14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H22" s="6" t="s">
+      <c r="D24" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I22" s="9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>72</v>
+      <c r="F24" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>76</v>
+      <c r="A25" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1809,76 +1932,76 @@
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>61</v>
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>46</v>
+      <c r="A2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>79</v>
+      <c r="A3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>53</v>
+      <c r="A4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>81</v>
+      <c r="A5" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>82</v>
+      <c r="A6" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>83</v>
+      <c r="A7" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>58</v>
+      <c r="A8" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>84</v>
+      <c r="A9" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>85</v>
+      <c r="A10" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>86</v>
+      <c r="A11" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/documentos/modelo_dicionario_de_dados.xlsx
+++ b/documentos/modelo_dicionario_de_dados.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="137">
   <si>
     <t xml:space="preserve">MODELO DE DICIONÁRIO DE DADOS</t>
   </si>
@@ -33,9 +33,15 @@
     <t xml:space="preserve">Projeto / Sistema:</t>
   </si>
   <si>
+    <t xml:space="preserve">TECHFIX</t>
+  </si>
+  <si>
     <t xml:space="preserve">Autor / Aluno:</t>
   </si>
   <si>
+    <t xml:space="preserve">Lucas Assumpção</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data de Criação:</t>
   </si>
   <si>
@@ -96,7 +102,7 @@
     <t xml:space="preserve"> Chave primária de identificação do funcionário.</t>
   </si>
   <si>
-    <t xml:space="preserve">nome</t>
+    <t xml:space="preserve">nome_funcionario</t>
   </si>
   <si>
     <t xml:space="preserve">TEXT</t>
@@ -105,24 +111,138 @@
     <t xml:space="preserve">Campo do nome do funcionário.</t>
   </si>
   <si>
+    <t xml:space="preserve">cadastrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">datetime(‘now’,’localtime)’</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de data de cadastro funcionário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de status funcionário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABELA CARGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de entrada de chave FK.</t>
+  </si>
+  <si>
     <t xml:space="preserve">cliente</t>
   </si>
   <si>
     <t xml:space="preserve">Chave primária de identificação do cliente.</t>
   </si>
   <si>
+    <t xml:space="preserve">nome_cliente</t>
+  </si>
+  <si>
     <t xml:space="preserve">Campo do nome do cliente.</t>
   </si>
   <si>
+    <t xml:space="preserve">Campo de data de cadastro cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de cpf do cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">telefone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de telefone do cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de status cliente.</t>
+  </si>
+  <si>
     <t xml:space="preserve">equipamento</t>
   </si>
   <si>
     <t xml:space="preserve">Chave primária de identificação do equipamento.</t>
   </si>
   <si>
+    <t xml:space="preserve">nome_equipamento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Campo do nome do equipamento.</t>
   </si>
   <si>
+    <t xml:space="preserve">id_marca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_tipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de status equipamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preco_servico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de preco do serviço.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">serie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de numero de serie do equipamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de data de cadastro equipamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primária de identificação do cargo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nome_cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo do nome do cargo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de data de cadastro do cargo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de status do cargo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">situacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primária de identificação de situacao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nome_situação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de nome da situação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de status da situação.</t>
+  </si>
+  <si>
     <t xml:space="preserve">INSTRUÇÕES E EXEMPLO PRÁTICO</t>
   </si>
   <si>
@@ -228,9 +348,6 @@
     <t xml:space="preserve">Nome civil completo do aluno.</t>
   </si>
   <si>
-    <t xml:space="preserve">cpf</t>
-  </si>
-  <si>
     <t xml:space="preserve">Apenas números. Deve ser único (UNIQUE).</t>
   </si>
   <si>
@@ -256,9 +373,6 @@
   </si>
   <si>
     <t xml:space="preserve">id_turma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FK</t>
   </si>
   <si>
     <t xml:space="preserve">tb_turmas(id_turma)</t>
@@ -808,7 +922,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
@@ -835,692 +949,1041 @@
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5"/>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="11"/>
       <c r="I11" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="10" t="s">
-        <v>28</v>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="11"/>
+      <c r="I12" s="14" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="H13" s="11"/>
       <c r="I13" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
+      <c r="C17" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
+      <c r="F17" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="G17" s="12"/>
       <c r="H17" s="11"/>
-      <c r="I17" s="14"/>
+      <c r="I17" s="14" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="10"/>
+      <c r="A18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="14" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
+      <c r="A19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="12"/>
+      <c r="F19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>36</v>
+      </c>
       <c r="H19" s="11"/>
-      <c r="I19" s="14"/>
+      <c r="I19" s="14" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="10"/>
+      <c r="A20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11"/>
+      <c r="I20" s="14" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="14"/>
+      <c r="A21" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="10"/>
+      <c r="A22" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="12"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="14" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
+      <c r="A23" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
+      <c r="E23" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="G23" s="12"/>
       <c r="H23" s="11"/>
-      <c r="I23" s="14"/>
+      <c r="I23" s="14" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="10"/>
+      <c r="A24" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="12"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="14" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
+      <c r="A25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
+      <c r="E25" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="G25" s="12"/>
       <c r="H25" s="11"/>
-      <c r="I25" s="14"/>
+      <c r="I25" s="14" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="8"/>
+      <c r="F26" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="H26" s="7"/>
-      <c r="I26" s="10"/>
+      <c r="I26" s="14" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="12"/>
+      <c r="A27" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
+      <c r="F27" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="G27" s="12"/>
       <c r="H27" s="11"/>
-      <c r="I27" s="14"/>
+      <c r="I27" s="14" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="8"/>
+      <c r="A28" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="8"/>
+      <c r="F28" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="H28" s="7"/>
-      <c r="I28" s="10"/>
+      <c r="I28" s="10" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
+      <c r="A29" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
+      <c r="F29" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="G29" s="12"/>
       <c r="H29" s="11"/>
-      <c r="I29" s="14"/>
+      <c r="I29" s="14" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="10"/>
+      <c r="A30" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="11"/>
+      <c r="I30" s="10" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="14"/>
+      <c r="A31" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="8"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="10"/>
+      <c r="A32" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="12"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="14" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="14"/>
+      <c r="A33" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="7"/>
+      <c r="I33" s="10" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="10"/>
+      <c r="A34" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="11"/>
+      <c r="I34" s="10" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="14"/>
+      <c r="A35" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="8"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="10" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="10"/>
+      <c r="A36" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" s="12"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="10" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="14"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="10"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="14"/>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="14"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="10"/>
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="14"/>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="14"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="10"/>
+      <c r="A42" s="11"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="14"/>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="11"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="14"/>
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="10"/>
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="14"/>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="14"/>
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="10"/>
+      <c r="A46" s="11"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="14"/>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="11"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="14"/>
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="10"/>
+      <c r="A48" s="11"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="14"/>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="14"/>
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="10"/>
+      <c r="A50" s="11"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="14"/>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="11"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="14"/>
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="10"/>
+      <c r="A52" s="11"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="14"/>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="11"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="14"/>
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="10"/>
+      <c r="A54" s="11"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="14"/>
     </row>
     <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="14"/>
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="10"/>
+      <c r="A56" s="11"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="14"/>
     </row>
     <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="14"/>
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="10"/>
+      <c r="A58" s="11"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="14"/>
     </row>
     <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="11"/>
-      <c r="I59" s="14"/>
+      <c r="A59" s="7"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="10"/>
+    </row>
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="11"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="14"/>
+    </row>
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="7"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="10"/>
+    </row>
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="11"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="14"/>
+    </row>
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="10"/>
+    </row>
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="11"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="14"/>
+    </row>
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="10"/>
+    </row>
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="11"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="14"/>
+    </row>
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="7"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="10"/>
+    </row>
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="11"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C10:C59" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C10:C68" type="list">
       <formula1>Validações!$A$1:$A$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E10:E59" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E10:E68" type="list">
       <formula1>Validações!$B$1:$B$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F10:F59" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F10:F68" type="list">
       <formula1>Validações!$C$1:$C$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1555,361 +2018,361 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1933,75 +2396,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/documentos/modelo_dicionario_de_dados.xlsx
+++ b/documentos/modelo_dicionario_de_dados.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="161">
   <si>
     <t xml:space="preserve">MODELO DE DICIONÁRIO DE DADOS</t>
   </si>
@@ -156,198 +156,273 @@
     <t xml:space="preserve">Campo de data de cadastro cliente.</t>
   </si>
   <si>
+    <t xml:space="preserve">id_funcionario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNCIONARIO/ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_funcionario_cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHECK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNCIONARIO_CARGO/ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-mail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de telefone do cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de status cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">equipamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primária de identificação do equipamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nome_equipamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo do nome do equipamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_marca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCA/ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIENTE/ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MODELO/ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_tipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIPO/ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de status equipamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">serie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de numero de serie do equipamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de numero de IMEI do equipamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de data de cadastro equipamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primária de identificação do cargo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nome_cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo do nome do cargo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de status do cargo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">situacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primária de identificação de situacao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nome_situação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de nome da situação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de status da situação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de data de cadastro situacao.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primária de identificação da marca.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nome_marca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo do nome do marca.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de status do marca.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primária de identificação do modelo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nome_modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo do nome do mdelo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de status do modelo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave primária de identificação do tipo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nome_tipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo do nome do tipo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de status do tipo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTRUÇÕES E EXEMPLO PRÁTICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como preencher o Dicionário de Dados e Exemplo Demonstrativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nome da Tabela:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificador da tabela em minúsculas/snake_case (ex: alunos, cursos).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Nome do Campo:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome exato da coluna no banco de dados (ex: id_aluno, cpf, data_nascimento).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Tipo de Dado:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo do atributo no SGBD (ex: INT, VARCHAR, DECIMAL, DATE). Use a lista suspensa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Tamanho / Precisão:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamanho do campo, se aplicável (ex: 100 para VARCHAR, 10,2 para DECIMAL).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Chave (PK/FK):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informe se o campo é Chave Primária (PK), Chave Estrangeira (FK), ou Ambos (PFK).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Permite Nulo?:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selecione SIM se aceitar valores nulos (NULL) ou NÃO se for NOT NULL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Valor Padrão:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor atribuído automaticamente caso nenhum seja informado (ex: CURRENT_TIMESTAMP, 0, 'ATIVO').</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Tabela Referenciada:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caso seja FK, informe a tabela e campo de origem (ex: cursos(id_curso)).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Descrição / Regra:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explicação clara do significado do dado e eventuais restrições ou regras de negócio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exemplo Preenchido:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome do Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor Padrão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabela / Campo Referenciado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tb_alunos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_aluno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTO_INCREMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificador único do aluno.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nome_completo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARCHAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome civil completo do aluno.</t>
+  </si>
+  <si>
     <t xml:space="preserve">cpf</t>
   </si>
   <si>
-    <t xml:space="preserve">Campo de cpf do cliente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">telefone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo de telefone do cliente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo de status cliente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">equipamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chave primária de identificação do equipamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nome_equipamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo do nome do equipamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id_marca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id_modelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id_tipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo de status equipamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preco_servico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo de preco do serviço.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">serie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo de numero de serie do equipamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo de data de cadastro equipamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cargo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chave primária de identificação do cargo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nome_cargo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo do nome do cargo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo de data de cadastro do cargo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo de status do cargo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">situacao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chave primária de identificação de situacao.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nome_situação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo de nome da situação.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo de status da situação.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSTRUÇÕES E EXEMPLO PRÁTICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como preencher o Dicionário de Dados e Exemplo Demonstrativo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Nome da Tabela:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identificador da tabela em minúsculas/snake_case (ex: alunos, cursos).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Nome do Campo:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome exato da coluna no banco de dados (ex: id_aluno, cpf, data_nascimento).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Tipo de Dado:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipo do atributo no SGBD (ex: INT, VARCHAR, DECIMAL, DATE). Use a lista suspensa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Tamanho / Precisão:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tamanho do campo, se aplicável (ex: 100 para VARCHAR, 10,2 para DECIMAL).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Chave (PK/FK):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Informe se o campo é Chave Primária (PK), Chave Estrangeira (FK), ou Ambos (PFK).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Permite Nulo?:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selecione SIM se aceitar valores nulos (NULL) ou NÃO se for NOT NULL.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Valor Padrão:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor atribuído automaticamente caso nenhum seja informado (ex: CURRENT_TIMESTAMP, 0, 'ATIVO').</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Tabela Referenciada:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caso seja FK, informe a tabela e campo de origem (ex: cursos(id_curso)).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. Descrição / Regra:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explicação clara do significado do dado e eventuais restrições ou regras de negócio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exemplo Preenchido:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome do Campo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor Padrão</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabela / Campo Referenciado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tb_alunos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id_aluno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTO_INCREMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identificador único do aluno.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nome_completo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VARCHAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nenhum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome civil completo do aluno.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Apenas números. Deve ser único (UNIQUE).</t>
   </si>
   <si>
@@ -361,9 +436,6 @@
   </si>
   <si>
     <t xml:space="preserve">email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIM</t>
   </si>
   <si>
     <t xml:space="preserve">NULL</t>
@@ -922,7 +994,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
@@ -1106,7 +1178,7 @@
         <v>34</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13" t="s">
@@ -1186,7 +1258,9 @@
       <c r="F17" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="12"/>
+      <c r="G17" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="H17" s="11"/>
       <c r="I17" s="14" t="s">
         <v>43</v>
@@ -1200,19 +1274,21 @@
         <v>44</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
+      <c r="E18" s="13" t="s">
+        <v>35</v>
+      </c>
       <c r="F18" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="11"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="I18" s="14" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1223,19 +1299,23 @@
         <v>46</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
+      <c r="E19" s="13" t="s">
+        <v>35</v>
+      </c>
       <c r="F19" s="13" t="s">
         <v>23</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="H19" s="11"/>
+        <v>47</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="I19" s="14" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1243,102 +1323,102 @@
         <v>39</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
-      <c r="F20" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>1</v>
+      <c r="F20" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9" t="s">
+      <c r="C22" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="8" t="s">
+      <c r="F22" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H21" s="7"/>
-      <c r="I21" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="12"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="14" t="s">
-        <v>52</v>
+      <c r="H22" s="7"/>
+      <c r="I22" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>27</v>
       </c>
       <c r="D23" s="13"/>
-      <c r="E23" s="13" t="s">
-        <v>35</v>
-      </c>
+      <c r="E23" s="13"/>
       <c r="F23" s="13" t="s">
         <v>23</v>
       </c>
       <c r="G23" s="12"/>
       <c r="H23" s="11"/>
       <c r="I23" s="14" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="13" t="s">
@@ -1348,20 +1428,22 @@
         <v>23</v>
       </c>
       <c r="G24" s="12"/>
-      <c r="H24" s="11"/>
+      <c r="H24" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="I24" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="13" t="s">
@@ -1370,62 +1452,72 @@
       <c r="F25" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="11"/>
+      <c r="G25" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="I25" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13" t="s">
+        <v>35</v>
+      </c>
       <c r="F26" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="7"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="11" t="s">
+        <v>61</v>
+      </c>
       <c r="I26" s="14" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
+      <c r="E27" s="13" t="s">
+        <v>35</v>
+      </c>
       <c r="F27" s="13" t="s">
         <v>23</v>
       </c>
       <c r="G27" s="12"/>
-      <c r="H27" s="11"/>
+      <c r="H27" s="11" t="s">
+        <v>63</v>
+      </c>
       <c r="I27" s="14" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>21</v>
@@ -1435,555 +1527,836 @@
       <c r="F28" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G28" s="8" t="s">
-        <v>36</v>
+      <c r="G28" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H28" s="7"/>
-      <c r="I28" s="10" t="s">
-        <v>60</v>
+      <c r="I28" s="14" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>29</v>
+        <v>52</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
+        <v>21</v>
+      </c>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
       <c r="F29" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G29" s="12"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="14" t="s">
-        <v>61</v>
+      <c r="G29" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H29" s="7"/>
+      <c r="I29" s="10" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>20</v>
+        <v>52</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13" t="s">
-        <v>22</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
       <c r="F30" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="11"/>
+        <v>68</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H30" s="7"/>
       <c r="I30" s="10" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
       <c r="F31" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G31" s="8"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="10" t="s">
-        <v>65</v>
+      <c r="G31" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" s="11"/>
+      <c r="I31" s="14" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>29</v>
+        <v>71</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>20</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
+      <c r="E32" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="F32" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G32" s="12"/>
+      <c r="G32" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="H32" s="11"/>
-      <c r="I32" s="14" t="s">
-        <v>66</v>
+      <c r="I32" s="10" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>32</v>
+        <v>71</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G33" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="G33" s="8"/>
       <c r="H33" s="7"/>
       <c r="I33" s="10" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13" t="s">
-        <v>22</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
       <c r="F34" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G34" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H34" s="11"/>
+      <c r="G34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="7"/>
       <c r="I34" s="10" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
+        <v>76</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="F35" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G35" s="8"/>
-      <c r="H35" s="7"/>
+      <c r="G35" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="11"/>
       <c r="I35" s="10" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B36" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" s="8"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G36" s="12"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="10"/>
+      <c r="C37" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" s="12"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="10" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="14"/>
+      <c r="A38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H38" s="7"/>
+      <c r="I38" s="14" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="10"/>
+      <c r="A39" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="11"/>
+      <c r="I39" s="10" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="14"/>
+      <c r="A40" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" s="8"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="10" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="8"/>
+      <c r="A41" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="8"/>
+      <c r="F41" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="H41" s="7"/>
-      <c r="I41" s="10"/>
+      <c r="I41" s="10" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="12"/>
+      <c r="A42" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
+      <c r="E42" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="G42" s="12"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="14"/>
+      <c r="H42" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="10"/>
+      <c r="A43" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="12"/>
+      <c r="A44" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="12"/>
+      <c r="E44" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="H44" s="11"/>
-      <c r="I44" s="14"/>
+      <c r="I44" s="10" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="8"/>
+      <c r="A45" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
+      <c r="F45" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="G45" s="8"/>
       <c r="H45" s="7"/>
-      <c r="I45" s="10"/>
+      <c r="I45" s="10" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="14"/>
+      <c r="A46" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="7"/>
+      <c r="I46" s="10" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="10"/>
+      <c r="A47" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="12"/>
+      <c r="H47" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="11"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12"/>
+      <c r="A48" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="14"/>
+      <c r="E48" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="10"/>
+      <c r="A49" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="11"/>
+      <c r="I49" s="10" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="11"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="14"/>
+      <c r="A50" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" s="8"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="10" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="8"/>
+      <c r="A51" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="8"/>
+      <c r="F51" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="H51" s="7"/>
-      <c r="I51" s="10"/>
+      <c r="I51" s="10" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="11"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="12"/>
+      <c r="A52" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
+      <c r="E52" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="G52" s="12"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="14"/>
+      <c r="H52" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I52" s="14" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="10"/>
+      <c r="A53" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I53" s="14" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="11"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="14"/>
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="10"/>
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="14"/>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="11"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="14"/>
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="10"/>
+      <c r="A57" s="11"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="14"/>
     </row>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="11"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="14"/>
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="10"/>
+      <c r="A59" s="11"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="14"/>
     </row>
     <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="11"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="11"/>
-      <c r="I60" s="14"/>
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="10"/>
+      <c r="A61" s="11"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="14"/>
     </row>
     <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="11"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="11"/>
-      <c r="I62" s="14"/>
+      <c r="A62" s="7"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="7"/>
-      <c r="I63" s="10"/>
+      <c r="A63" s="11"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="14"/>
     </row>
     <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="11"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="11"/>
-      <c r="I64" s="14"/>
+      <c r="A64" s="7"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="7"/>
-      <c r="I65" s="10"/>
+      <c r="A65" s="11"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="14"/>
     </row>
     <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="11"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="11"/>
-      <c r="I66" s="14"/>
+      <c r="A66" s="7"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="10"/>
+      <c r="A67" s="11"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="14"/>
     </row>
     <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="11"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="11"/>
-      <c r="I68" s="14"/>
+      <c r="A68" s="7"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="10"/>
+    </row>
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="11"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="14"/>
+    </row>
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="7"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="10"/>
+    </row>
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="11"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="14"/>
+    </row>
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="7"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="10"/>
+    </row>
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="11"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C10:C68" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C10:C73" type="list">
       <formula1>Validações!$A$1:$A$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E10:E68" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E10:E73" type="list">
       <formula1>Validações!$B$1:$B$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F10:F68" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F10:F73" type="list">
       <formula1>Validações!$C$1:$C$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2018,89 +2391,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2108,7 +2481,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>12</v>
@@ -2123,10 +2496,10 @@
         <v>15</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>18</v>
@@ -2134,16 +2507,16 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>22</v>
@@ -2152,131 +2525,131 @@
         <v>23</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="F19" s="13" t="s">
         <v>23</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>35</v>
@@ -2285,27 +2658,27 @@
         <v>23</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>22</v>
@@ -2314,65 +2687,65 @@
         <v>23</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="F25" s="13" t="s">
         <v>23</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2402,12 +2775,12 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>35</v>
@@ -2418,23 +2791,23 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2444,27 +2817,27 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/documentos/modelo_dicionario_de_dados.xlsx
+++ b/documentos/modelo_dicionario_de_dados.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="162">
   <si>
     <t xml:space="preserve">MODELO DE DICIONÁRIO DE DADOS</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t xml:space="preserve">Campo de status do marca.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHECK (1,2)</t>
   </si>
   <si>
     <t xml:space="preserve">modelo</t>
@@ -1875,7 +1878,7 @@
         <v>23</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="H43" s="11" t="s">
         <v>48</v>
@@ -1886,7 +1889,7 @@
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>20</v>
@@ -1906,15 +1909,15 @@
       </c>
       <c r="H44" s="11"/>
       <c r="I44" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>27</v>
@@ -1927,12 +1930,12 @@
       <c r="G45" s="8"/>
       <c r="H45" s="7"/>
       <c r="I45" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>32</v>
@@ -1950,12 +1953,12 @@
       </c>
       <c r="H46" s="7"/>
       <c r="I46" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>44</v>
@@ -1980,7 +1983,7 @@
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>46</v>
@@ -2007,7 +2010,7 @@
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B49" s="15" t="s">
         <v>20</v>
@@ -2027,15 +2030,15 @@
       </c>
       <c r="H49" s="11"/>
       <c r="I49" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>27</v>
@@ -2048,12 +2051,12 @@
       <c r="G50" s="8"/>
       <c r="H50" s="7"/>
       <c r="I50" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>32</v>
@@ -2071,12 +2074,12 @@
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>44</v>
@@ -2101,7 +2104,7 @@
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>46</v>
@@ -2391,89 +2394,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2481,7 +2484,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>12</v>
@@ -2496,10 +2499,10 @@
         <v>15</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>18</v>
@@ -2507,16 +2510,16 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>22</v>
@@ -2525,131 +2528,131 @@
         <v>23</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F19" s="13" t="s">
         <v>23</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F21" s="13" t="s">
         <v>68</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>35</v>
@@ -2658,27 +2661,27 @@
         <v>23</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>22</v>
@@ -2687,65 +2690,65 @@
         <v>23</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F25" s="13" t="s">
         <v>23</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -2780,7 +2783,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>35</v>
@@ -2791,23 +2794,23 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2817,27 +2820,27 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/documentos/modelo_dicionario_de_dados.xlsx
+++ b/documentos/modelo_dicionario_de_dados.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="162">
   <si>
     <t xml:space="preserve">MODELO DE DICIONÁRIO DE DADOS</t>
   </si>
@@ -997,7 +997,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
@@ -1608,118 +1608,124 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>20</v>
+      <c r="A32" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="13" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G32" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="11"/>
-      <c r="I32" s="10" t="s">
-        <v>72</v>
+      <c r="G32" s="12"/>
+      <c r="H32" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
+      <c r="A33" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13" t="s">
+        <v>35</v>
+      </c>
       <c r="F33" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G33" s="8"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="10" t="s">
-        <v>74</v>
+      <c r="G33" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="B34" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
+      <c r="B34" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="F34" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G34" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="7"/>
+      <c r="G34" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="11"/>
       <c r="I34" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13" t="s">
-        <v>22</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
       <c r="F35" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G35" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" s="11"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="7"/>
       <c r="I35" s="10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>78</v>
+        <v>71</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G36" s="8"/>
+      <c r="G36" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="H36" s="7"/>
       <c r="I36" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1727,429 +1733,453 @@
         <v>76</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
+      <c r="E37" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="F37" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G37" s="12"/>
+      <c r="G37" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="H37" s="11"/>
       <c r="I37" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="11" t="s">
         <v>76</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
-      <c r="F38" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G38" s="12" t="s">
-        <v>30</v>
-      </c>
+      <c r="F38" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" s="8"/>
       <c r="H38" s="7"/>
-      <c r="I38" s="14" t="s">
-        <v>81</v>
+      <c r="I38" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>20</v>
+        <v>76</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D39" s="13"/>
-      <c r="E39" s="13" t="s">
-        <v>22</v>
-      </c>
+      <c r="E39" s="13"/>
       <c r="F39" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G39" s="12" t="s">
-        <v>24</v>
-      </c>
+      <c r="G39" s="12"/>
       <c r="H39" s="11"/>
       <c r="I39" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11" t="s">
-        <v>82</v>
+      <c r="A40" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
-      <c r="F40" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G40" s="8"/>
+      <c r="F40" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="H40" s="7"/>
-      <c r="I40" s="10" t="s">
-        <v>85</v>
+      <c r="I40" s="14" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="11"/>
+      <c r="I41" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="8"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C41" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G41" s="8" t="n">
+      <c r="C43" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="7"/>
-      <c r="I41" s="10" t="s">
+      <c r="H43" s="7"/>
+      <c r="I43" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7" t="s">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B44" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G42" s="12"/>
-      <c r="H42" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I42" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="H43" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I43" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>20</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="13" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F44" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G44" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H44" s="11"/>
-      <c r="I44" s="10" t="s">
-        <v>89</v>
+      <c r="G44" s="12"/>
+      <c r="H44" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
+      <c r="A45" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13" t="s">
+        <v>35</v>
+      </c>
       <c r="F45" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G45" s="8"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="10" t="s">
-        <v>91</v>
+      <c r="G45" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H46" s="11"/>
+      <c r="I46" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="8"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B48" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G46" s="8" t="n">
+      <c r="C48" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="7"/>
-      <c r="I46" s="10" t="s">
+      <c r="H48" s="7"/>
+      <c r="I48" s="10" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="s">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B49" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G47" s="12"/>
-      <c r="H47" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I47" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G48" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H48" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I48" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>20</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D49" s="13"/>
       <c r="E49" s="13" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F49" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G49" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H49" s="11"/>
-      <c r="I49" s="10" t="s">
-        <v>94</v>
+      <c r="G49" s="12"/>
+      <c r="H49" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
+      <c r="A50" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13" t="s">
+        <v>35</v>
+      </c>
       <c r="F50" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G50" s="8"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="10" t="s">
-        <v>96</v>
+      <c r="G50" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" s="11"/>
+      <c r="I51" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" s="8"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G51" s="8" t="n">
+      <c r="C53" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="7"/>
-      <c r="I51" s="10" t="s">
+      <c r="H53" s="7"/>
+      <c r="I53" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="s">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B54" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13" t="s">
+      <c r="C54" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F52" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G52" s="12"/>
-      <c r="H52" s="11" t="s">
+      <c r="F54" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G54" s="12"/>
+      <c r="H54" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="I52" s="14" t="s">
+      <c r="I54" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B55" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C53" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13" t="s">
+      <c r="C55" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F53" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G53" s="12" t="s">
+      <c r="F55" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H53" s="11" t="s">
+      <c r="H55" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I53" s="14" t="s">
+      <c r="I55" s="14" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="10"/>
-    </row>
-    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="14"/>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7"/>
@@ -2349,17 +2379,39 @@
       <c r="H73" s="11"/>
       <c r="I73" s="14"/>
     </row>
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="7"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="9"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="10"/>
+    </row>
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="11"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="14"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C10:C73" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C10:C75" type="list">
       <formula1>Validações!$A$1:$A$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E10:E73" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E10:E75" type="list">
       <formula1>Validações!$B$1:$B$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F10:F73" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F10:F75" type="list">
       <formula1>Validações!$C$1:$C$2</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/documentos/modelo_dicionario_de_dados.xlsx
+++ b/documentos/modelo_dicionario_de_dados.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="224">
   <si>
     <t xml:space="preserve">MODELO DE DICIONÁRIO DE DADOS</t>
   </si>
@@ -126,6 +126,9 @@
     <t xml:space="preserve">Campo de status funcionário</t>
   </si>
   <si>
+    <t xml:space="preserve">Chave primária de identificação do funcionário.</t>
+  </si>
+  <si>
     <t xml:space="preserve">id_cargo</t>
   </si>
   <si>
@@ -316,6 +319,189 @@
   </si>
   <si>
     <t xml:space="preserve">Campo de status do tipo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forma_pagamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nome_forma_pagamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data_cadastro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">categoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nome_categoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ordem_situacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_ordem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORDEM/ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_situacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SITUACAO/ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_tecnico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_tecnico_cargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHECK(3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data_situacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pecas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nome_pecas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_categoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CATEGORIA/ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preco_compra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de preço de compra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preco_venda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de preço de venda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estoque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de quantidade em estoque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ordem_pecas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_pecas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quantidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de quantidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor_unitario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de valor unitario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ordem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_equipamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EQUIPAMENTO/ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_funcionario_abertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_funcionario_cargo_abertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data_abertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de data de abertura de servico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_situacao_atual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data_fechamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de data de fechamento de servico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">descricao_defeito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de descrição do defeito pelo cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">descricao_constatado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de descrição do defeito pelo técnico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de valor total.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_forma_pagamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORMA_PAGAMENTO/ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ordem_servico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_servico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de data de ordem de serviço.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">servicos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nome_servico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de data de servico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHECK(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de preco do servico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hora_trabalhada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de hora trabalhada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo de status do servico.</t>
   </si>
   <si>
     <t xml:space="preserve">INSTRUÇÕES E EXEMPLO PRÁTICO</t>
@@ -517,7 +703,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -578,13 +764,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Consolas"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="10"/>
       <name val="Consolas"/>
       <family val="0"/>
@@ -668,7 +847,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -729,8 +908,12 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -741,7 +924,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -997,7 +1180,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
@@ -1174,1244 +1357,2660 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="16"/>
+      <c r="I14" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="16"/>
+      <c r="I16" s="15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="16"/>
+      <c r="I17" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="12" t="s">
+      <c r="C18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="16"/>
+      <c r="E18" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="F18" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="H18" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="I18" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="15" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9" t="s">
+      <c r="C19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="16"/>
+      <c r="E19" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="8" t="s">
+      <c r="F19" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="10" t="s">
+      <c r="H19" s="16"/>
+      <c r="I19" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
+      <c r="B20" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="16"/>
+      <c r="I21" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="E22" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="16"/>
+      <c r="H22" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="12" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="16"/>
+      <c r="E23" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="12"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" s="16"/>
+      <c r="I24" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="16"/>
+      <c r="I25" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="16"/>
+      <c r="E26" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="16"/>
+      <c r="I26" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="16"/>
+      <c r="E28" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="16"/>
+      <c r="H28" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="I28" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="11" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="16"/>
+      <c r="E29" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="16"/>
+      <c r="E30" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="16"/>
+      <c r="H30" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="16"/>
+      <c r="E31" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="16"/>
+      <c r="H31" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="16"/>
+      <c r="I32" s="15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H33" s="16"/>
+      <c r="I33" s="15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H34" s="16"/>
+      <c r="I34" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C35" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="12" t="s">
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="H35" s="16"/>
+      <c r="I35" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="16"/>
+      <c r="E36" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" s="16"/>
+      <c r="H36" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I36" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="12"/>
-      <c r="H18" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="16"/>
+      <c r="E37" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I37" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="12" t="s">
+    </row>
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="16"/>
+      <c r="E38" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="16"/>
+      <c r="I38" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" s="11"/>
-      <c r="I20" s="14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="11" t="s">
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B40" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="12" t="n">
+      <c r="C40" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="11"/>
-      <c r="I21" s="14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="7"/>
-      <c r="I22" s="10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="12"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="12"/>
-      <c r="H26" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I26" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G27" s="12"/>
-      <c r="H27" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="7"/>
-      <c r="I28" s="14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H29" s="7"/>
-      <c r="I29" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H30" s="7"/>
-      <c r="I30" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H31" s="11"/>
-      <c r="I31" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G32" s="12"/>
-      <c r="H32" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I32" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I33" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H34" s="11"/>
-      <c r="I34" s="10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G35" s="8"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G36" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="7"/>
-      <c r="I36" s="10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="11" t="s">
+      <c r="H40" s="16"/>
+      <c r="I40" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H37" s="11"/>
-      <c r="I37" s="10" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="15" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G38" s="8"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G39" s="12"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G40" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H40" s="7"/>
-      <c r="I40" s="14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="11" t="s">
-        <v>82</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13" t="s">
+      <c r="C41" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" s="16"/>
+      <c r="E41" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F41" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G41" s="12" t="s">
+      <c r="F41" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H41" s="11"/>
-      <c r="I41" s="10" t="s">
+      <c r="H41" s="16"/>
+      <c r="I41" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H42" s="16"/>
+      <c r="I42" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="16"/>
+      <c r="I43" s="15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H44" s="16"/>
+      <c r="I44" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="15" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="7" t="s">
+      <c r="B45" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="16"/>
+      <c r="E45" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="16"/>
+      <c r="I45" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="8" t="s">
+    </row>
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C46" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G42" s="8"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B43" s="11" t="s">
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G43" s="8" t="n">
+      <c r="C47" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="7"/>
-      <c r="I43" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G44" s="12"/>
-      <c r="H44" s="11" t="s">
+      <c r="H47" s="16"/>
+      <c r="I47" s="15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B48" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="I44" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B45" s="11" t="s">
+      <c r="C48" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="16"/>
+      <c r="E48" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" s="16"/>
+      <c r="H48" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="H45" s="11" t="s">
+      <c r="I48" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" s="16"/>
+      <c r="E49" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H49" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I49" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="16"/>
+      <c r="E50" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H50" s="16"/>
+      <c r="I50" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="16"/>
+      <c r="I52" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="16"/>
+      <c r="E53" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53" s="16"/>
+      <c r="H53" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I53" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="16"/>
+      <c r="E54" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G54" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="I45" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B46" s="15" t="s">
+      <c r="H54" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I54" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B55" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C46" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13" t="s">
+      <c r="C55" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" s="16"/>
+      <c r="E55" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F46" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G46" s="12" t="s">
+      <c r="F55" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H46" s="11"/>
-      <c r="I46" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" s="8" t="s">
+      <c r="H55" s="16"/>
+      <c r="I55" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G47" s="8"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B48" s="11" t="s">
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" s="16"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B57" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G48" s="8" t="n">
+      <c r="C57" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="7"/>
-      <c r="I48" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G49" s="12"/>
-      <c r="H49" s="11" t="s">
+      <c r="H57" s="16"/>
+      <c r="I57" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B58" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="I49" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B50" s="11" t="s">
+      <c r="C58" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="16"/>
+      <c r="E58" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G58" s="16"/>
+      <c r="H58" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G50" s="12" t="s">
+      <c r="I58" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B59" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="C59" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="16"/>
+      <c r="E59" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="I50" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B51" s="15" t="s">
+      <c r="H59" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I59" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B60" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C51" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13" t="s">
+      <c r="C60" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" s="16"/>
+      <c r="E60" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F51" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G51" s="12" t="s">
+      <c r="F60" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H51" s="11"/>
-      <c r="I51" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B52" s="7" t="s">
+      <c r="H60" s="16"/>
+      <c r="I60" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C52" s="8" t="s">
+    </row>
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C61" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G52" s="8"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B53" s="11" t="s">
+      <c r="D61" s="16"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G61" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H61" s="16"/>
+      <c r="I61" s="15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="16"/>
+      <c r="E62" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F62" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" s="16"/>
+      <c r="H62" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I62" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="16"/>
+      <c r="E63" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G63" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H63" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I63" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G64" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H64" s="16"/>
+      <c r="I64" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B65" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C53" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G53" s="8" t="n">
+      <c r="C65" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" s="16"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G65" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H53" s="7"/>
-      <c r="I53" s="10" t="s">
+      <c r="H65" s="16"/>
+      <c r="I65" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D66" s="16"/>
+      <c r="E66" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F66" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G66" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H66" s="16"/>
+      <c r="I66" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G67" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="16"/>
+      <c r="I67" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68" s="16"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G68" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H68" s="16"/>
+      <c r="I68" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H69" s="16"/>
+      <c r="I69" s="15" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G54" s="12"/>
-      <c r="H54" s="11" t="s">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B70" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="I54" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B55" s="11" t="s">
+      <c r="C70" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="16"/>
+      <c r="E70" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F70" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G70" s="16"/>
+      <c r="H70" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C55" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F55" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G55" s="12" t="s">
+      <c r="I70" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B71" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="C71" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="16"/>
+      <c r="E71" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="10"/>
-    </row>
-    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="14"/>
-    </row>
-    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="10"/>
-    </row>
-    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="11"/>
-      <c r="I59" s="14"/>
-    </row>
-    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="10"/>
-    </row>
-    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="14"/>
-    </row>
-    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="10"/>
-    </row>
-    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="11"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="11"/>
-      <c r="I63" s="14"/>
-    </row>
-    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="10"/>
-    </row>
-    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="14"/>
-    </row>
-    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="7"/>
-      <c r="I66" s="10"/>
-    </row>
-    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="11"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="11"/>
-      <c r="I67" s="14"/>
-    </row>
-    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="10"/>
-    </row>
-    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="11"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="11"/>
-      <c r="I69" s="14"/>
-    </row>
-    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="10"/>
-    </row>
-    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="11"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="11"/>
-      <c r="I71" s="14"/>
+      <c r="H71" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I71" s="15" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="10"/>
+      <c r="A72" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" s="16"/>
+      <c r="E72" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F72" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G72" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H72" s="16"/>
+      <c r="I72" s="15" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="11"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="11"/>
-      <c r="I73" s="14"/>
+      <c r="A73" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D73" s="16"/>
+      <c r="E73" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G73" s="16"/>
+      <c r="H73" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="I73" s="15" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="10"/>
+      <c r="A74" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="16"/>
+      <c r="E74" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F74" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G74" s="16"/>
+      <c r="H74" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I74" s="15" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="11"/>
-      <c r="B75" s="11"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="11"/>
-      <c r="I75" s="14"/>
+      <c r="A75" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" s="16"/>
+      <c r="E75" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F75" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G75" s="16"/>
+      <c r="H75" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I75" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" s="16"/>
+      <c r="E76" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F76" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G76" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="H76" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I76" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G77" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H77" s="16"/>
+      <c r="I77" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D78" s="16"/>
+      <c r="E78" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F78" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G78" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H78" s="16"/>
+      <c r="I78" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G79" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H79" s="16"/>
+      <c r="I79" s="15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D80" s="16"/>
+      <c r="E80" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F80" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G80" s="16"/>
+      <c r="H80" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="I80" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D81" s="16"/>
+      <c r="E81" s="16"/>
+      <c r="F81" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G81" s="16"/>
+      <c r="H81" s="16"/>
+      <c r="I81" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D82" s="16"/>
+      <c r="E82" s="16"/>
+      <c r="F82" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G82" s="16"/>
+      <c r="H82" s="16"/>
+      <c r="I82" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B83" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G83" s="16"/>
+      <c r="H83" s="16"/>
+      <c r="I83" s="15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B84" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D84" s="16"/>
+      <c r="E84" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F84" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84" s="16"/>
+      <c r="H84" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I84" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D85" s="16"/>
+      <c r="E85" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F85" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G85" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H85" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I85" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B86" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C86" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D86" s="16"/>
+      <c r="E86" s="16"/>
+      <c r="F86" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G86" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H86" s="16"/>
+      <c r="I86" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" s="16"/>
+      <c r="E87" s="16"/>
+      <c r="F87" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G87" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="16"/>
+      <c r="I87" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B88" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" s="16"/>
+      <c r="E88" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F88" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G88" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H88" s="16"/>
+      <c r="I88" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B89" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C89" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D89" s="16"/>
+      <c r="E89" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F89" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G89" s="16"/>
+      <c r="H89" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="I89" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D90" s="16"/>
+      <c r="E90" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F90" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G90" s="16"/>
+      <c r="H90" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="I90" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B91" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C91" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D91" s="16"/>
+      <c r="E91" s="16"/>
+      <c r="F91" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G91" s="16"/>
+      <c r="H91" s="16"/>
+      <c r="I91" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B92" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92" s="16"/>
+      <c r="E92" s="16"/>
+      <c r="F92" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G92" s="16"/>
+      <c r="H92" s="16"/>
+      <c r="I92" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C93" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93" s="16"/>
+      <c r="E93" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F93" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G93" s="16"/>
+      <c r="H93" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I93" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" s="16"/>
+      <c r="E94" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F94" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G94" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H94" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I94" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B95" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C95" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D95" s="16"/>
+      <c r="E95" s="16"/>
+      <c r="F95" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G95" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H95" s="16"/>
+      <c r="I95" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C96" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D96" s="16"/>
+      <c r="E96" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F96" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G96" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" s="16"/>
+      <c r="I96" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B97" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97" s="16"/>
+      <c r="E97" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F97" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G97" s="16"/>
+      <c r="H97" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="I97" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B98" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" s="16"/>
+      <c r="E98" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F98" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G98" s="16"/>
+      <c r="H98" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I98" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B99" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D99" s="16"/>
+      <c r="E99" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F99" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G99" s="16"/>
+      <c r="H99" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I99" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B100" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D100" s="16"/>
+      <c r="E100" s="16"/>
+      <c r="F100" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G100" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H100" s="16"/>
+      <c r="I100" s="15" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B101" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="C101" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D101" s="16"/>
+      <c r="E101" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F101" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G101" s="16"/>
+      <c r="H101" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I101" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B102" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C102" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D102" s="16"/>
+      <c r="E102" s="16"/>
+      <c r="F102" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G102" s="16"/>
+      <c r="H102" s="16"/>
+      <c r="I102" s="15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B103" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C103" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D103" s="16"/>
+      <c r="E103" s="16"/>
+      <c r="F103" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G103" s="16"/>
+      <c r="H103" s="16"/>
+      <c r="I103" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B104" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C104" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D104" s="16"/>
+      <c r="E104" s="16"/>
+      <c r="F104" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G104" s="16"/>
+      <c r="H104" s="16"/>
+      <c r="I104" s="15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B105" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C105" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105" s="16"/>
+      <c r="E105" s="16"/>
+      <c r="F105" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G105" s="16"/>
+      <c r="H105" s="16"/>
+      <c r="I105" s="15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B106" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C106" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D106" s="16"/>
+      <c r="E106" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F106" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G106" s="16"/>
+      <c r="H106" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="I106" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B107" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C107" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D107" s="16"/>
+      <c r="E107" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F107" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G107" s="16"/>
+      <c r="H107" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I107" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B108" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C108" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D108" s="16"/>
+      <c r="E108" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F108" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G108" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="H108" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I108" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="B109" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D109" s="16"/>
+      <c r="E109" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F109" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G109" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H109" s="16"/>
+      <c r="I109" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="B110" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C110" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D110" s="16"/>
+      <c r="E110" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F110" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G110" s="16"/>
+      <c r="H110" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="I110" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="B111" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C111" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D111" s="16"/>
+      <c r="E111" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F111" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G111" s="16"/>
+      <c r="H111" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I111" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="B112" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C112" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D112" s="16"/>
+      <c r="E112" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F112" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G112" s="16"/>
+      <c r="H112" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I112" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="B113" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C113" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D113" s="16"/>
+      <c r="E113" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F113" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G113" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="H113" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I113" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="B114" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C114" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D114" s="16"/>
+      <c r="E114" s="16"/>
+      <c r="F114" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G114" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H114" s="16"/>
+      <c r="I114" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B115" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C115" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D115" s="16"/>
+      <c r="E115" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F115" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G115" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H115" s="16"/>
+      <c r="I115" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B116" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C116" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D116" s="16"/>
+      <c r="E116" s="16"/>
+      <c r="F116" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G116" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H116" s="16"/>
+      <c r="I116" s="15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B117" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C117" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D117" s="16"/>
+      <c r="E117" s="16"/>
+      <c r="F117" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G117" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H117" s="16"/>
+      <c r="I117" s="15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B118" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C118" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D118" s="16"/>
+      <c r="E118" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F118" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G118" s="16"/>
+      <c r="H118" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I118" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B119" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C119" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D119" s="16"/>
+      <c r="E119" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F119" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G119" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="H119" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I119" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B120" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C120" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D120" s="16"/>
+      <c r="E120" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F120" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G120" s="16"/>
+      <c r="H120" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I120" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B121" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C121" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" s="16"/>
+      <c r="E121" s="16"/>
+      <c r="F121" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G121" s="16"/>
+      <c r="H121" s="16"/>
+      <c r="I121" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B122" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C122" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D122" s="16"/>
+      <c r="E122" s="16"/>
+      <c r="F122" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G122" s="16"/>
+      <c r="H122" s="16"/>
+      <c r="I122" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B123" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C123" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D123" s="16"/>
+      <c r="E123" s="16"/>
+      <c r="F123" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G123" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" s="16"/>
+      <c r="I123" s="15" t="s">
+        <v>159</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C10:C75" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C10:C13" type="list">
       <formula1>Validações!$A$1:$A$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E10:E75" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E10:E13" type="list">
       <formula1>Validações!$B$1:$B$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F10:F75" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F10:F13" type="list">
       <formula1>Validações!$C$1:$C$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2446,89 +4045,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>101</v>
+      <c r="A4" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>103</v>
+      <c r="A5" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>105</v>
+      <c r="A6" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>107</v>
+      <c r="A7" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>109</v>
+      <c r="A8" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>111</v>
+      <c r="A9" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>113</v>
+      <c r="A10" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>115</v>
+      <c r="A11" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>117</v>
+      <c r="A12" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>118</v>
+      <c r="A14" s="19" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2536,7 +4135,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>12</v>
@@ -2551,10 +4150,10 @@
         <v>15</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>121</v>
+        <v>183</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>18</v>
@@ -2562,16 +4161,16 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>22</v>
@@ -2580,160 +4179,160 @@
         <v>23</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>127</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>132</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>133</v>
+        <v>195</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="F19" s="13" t="s">
         <v>23</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>134</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>135</v>
+        <v>197</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>136</v>
+        <v>198</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>137</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>138</v>
+        <v>200</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>140</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>144</v>
+        <v>206</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>22</v>
@@ -2742,65 +4341,65 @@
         <v>23</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>144</v>
+        <v>206</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>144</v>
+        <v>206</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="F25" s="13" t="s">
         <v>23</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2830,15 +4429,15 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>153</v>
+        <v>215</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>23</v>
@@ -2846,23 +4445,23 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>156</v>
+        <v>218</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>157</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2872,27 +4471,27 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>158</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>136</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>160</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>161</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/documentos/modelo_dicionario_de_dados.xlsx
+++ b/documentos/modelo_dicionario_de_dados.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="222">
   <si>
     <t xml:space="preserve">MODELO DE DICIONÁRIO DE DADOS</t>
   </si>
@@ -373,12 +373,6 @@
   </si>
   <si>
     <t xml:space="preserve">CATEGORIA/ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preco_compra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo de preço de compra</t>
   </si>
   <si>
     <t xml:space="preserve">preco_venda</t>
@@ -908,11 +902,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1180,7 +1174,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
@@ -3022,20 +3016,24 @@
         <v>113</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
+      <c r="E83" s="15" t="s">
+        <v>36</v>
+      </c>
       <c r="F83" s="15" t="s">
         <v>23</v>
       </c>
       <c r="G83" s="16"/>
-      <c r="H83" s="16"/>
+      <c r="H83" s="15" t="s">
+        <v>46</v>
+      </c>
       <c r="I83" s="15" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3043,7 +3041,7 @@
         <v>113</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>21</v>
@@ -3055,9 +3053,11 @@
       <c r="F84" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G84" s="16"/>
+      <c r="G84" s="15" t="s">
+        <v>48</v>
+      </c>
       <c r="H84" s="15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I84" s="15" t="s">
         <v>39</v>
@@ -3068,26 +3068,22 @@
         <v>113</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D85" s="16"/>
-      <c r="E85" s="15" t="s">
-        <v>36</v>
-      </c>
+      <c r="E85" s="16"/>
       <c r="F85" s="15" t="s">
         <v>23</v>
       </c>
       <c r="G85" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="H85" s="15" t="s">
-        <v>49</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="H85" s="16"/>
       <c r="I85" s="15" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3095,78 +3091,80 @@
         <v>113</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D86" s="16"/>
       <c r="E86" s="16"/>
       <c r="F86" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G86" s="15" t="s">
-        <v>30</v>
+      <c r="G86" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="H86" s="16"/>
       <c r="I86" s="15" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="15" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D87" s="16"/>
-      <c r="E87" s="16"/>
+      <c r="E87" s="15" t="s">
+        <v>22</v>
+      </c>
       <c r="F87" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G87" s="15" t="n">
-        <v>1</v>
+      <c r="G87" s="15" t="s">
+        <v>24</v>
       </c>
       <c r="H87" s="16"/>
       <c r="I87" s="15" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="C88" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D88" s="16"/>
       <c r="E88" s="15" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F88" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G88" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H88" s="16"/>
+      <c r="G88" s="16"/>
+      <c r="H88" s="15" t="s">
+        <v>106</v>
+      </c>
       <c r="I88" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>21</v>
@@ -3188,32 +3186,28 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B90" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="B90" s="15" t="s">
+      <c r="C90" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D90" s="16"/>
+      <c r="E90" s="16"/>
+      <c r="F90" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G90" s="16"/>
+      <c r="H90" s="16"/>
+      <c r="I90" s="15" t="s">
         <v>124</v>
-      </c>
-      <c r="C90" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D90" s="16"/>
-      <c r="E90" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F90" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="G90" s="16"/>
-      <c r="H90" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="I90" s="15" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B91" s="15" t="s">
         <v>125</v>
@@ -3234,31 +3228,35 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>127</v>
+        <v>45</v>
       </c>
       <c r="C92" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D92" s="16"/>
-      <c r="E92" s="16"/>
+      <c r="E92" s="15" t="s">
+        <v>36</v>
+      </c>
       <c r="F92" s="15" t="s">
         <v>23</v>
       </c>
       <c r="G92" s="16"/>
-      <c r="H92" s="16"/>
+      <c r="H92" s="15" t="s">
+        <v>46</v>
+      </c>
       <c r="I92" s="15" t="s">
-        <v>128</v>
+        <v>39</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C93" s="15" t="s">
         <v>21</v>
@@ -3270,9 +3268,11 @@
       <c r="F93" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G93" s="16"/>
+      <c r="G93" s="15" t="s">
+        <v>48</v>
+      </c>
       <c r="H93" s="15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I93" s="15" t="s">
         <v>39</v>
@@ -3280,82 +3280,80 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D94" s="16"/>
-      <c r="E94" s="15" t="s">
-        <v>36</v>
-      </c>
+      <c r="E94" s="16"/>
       <c r="F94" s="15" t="s">
         <v>23</v>
       </c>
       <c r="G94" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="H94" s="15" t="s">
-        <v>49</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="H94" s="16"/>
       <c r="I94" s="15" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="15" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D95" s="16"/>
-      <c r="E95" s="16"/>
+      <c r="E95" s="15" t="s">
+        <v>22</v>
+      </c>
       <c r="F95" s="15" t="s">
         <v>23</v>
       </c>
       <c r="G95" s="15" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H95" s="16"/>
       <c r="I95" s="15" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D96" s="16"/>
       <c r="E96" s="15" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F96" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G96" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H96" s="16"/>
+      <c r="G96" s="16"/>
+      <c r="H96" s="15" t="s">
+        <v>129</v>
+      </c>
       <c r="I96" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B97" s="15" t="s">
         <v>130</v>
@@ -3372,18 +3370,18 @@
       </c>
       <c r="G97" s="16"/>
       <c r="H97" s="15" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="I97" s="15" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C98" s="15" t="s">
         <v>21</v>
@@ -3403,82 +3401,78 @@
         <v>39</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B99" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D99" s="16"/>
+      <c r="E99" s="16"/>
+      <c r="F99" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G99" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H99" s="16"/>
+      <c r="I99" s="15" t="s">
         <v>133</v>
-      </c>
-      <c r="C99" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D99" s="16"/>
-      <c r="E99" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F99" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="G99" s="16"/>
-      <c r="H99" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I99" s="15" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B100" s="15" t="s">
         <v>134</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D100" s="16"/>
-      <c r="E100" s="16"/>
+      <c r="E100" s="15" t="s">
+        <v>36</v>
+      </c>
       <c r="F100" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G100" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="H100" s="16"/>
+      <c r="G100" s="16"/>
+      <c r="H100" s="15" t="s">
+        <v>108</v>
+      </c>
       <c r="I100" s="15" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B101" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C101" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D101" s="16"/>
+      <c r="E101" s="16"/>
+      <c r="F101" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G101" s="16"/>
+      <c r="H101" s="16"/>
+      <c r="I101" s="15" t="s">
         <v>136</v>
-      </c>
-      <c r="C101" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D101" s="16"/>
-      <c r="E101" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F101" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="G101" s="16"/>
-      <c r="H101" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I101" s="15" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B102" s="15" t="s">
         <v>137</v>
@@ -3499,7 +3493,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B103" s="15" t="s">
         <v>139</v>
@@ -3510,7 +3504,7 @@
       <c r="D103" s="16"/>
       <c r="E103" s="16"/>
       <c r="F103" s="15" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="G103" s="16"/>
       <c r="H103" s="16"/>
@@ -3520,18 +3514,18 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B104" s="15" t="s">
         <v>141</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D104" s="16"/>
       <c r="E104" s="16"/>
       <c r="F104" s="15" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="G104" s="16"/>
       <c r="H104" s="16"/>
@@ -3541,7 +3535,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B105" s="15" t="s">
         <v>143</v>
@@ -3550,22 +3544,26 @@
         <v>21</v>
       </c>
       <c r="D105" s="16"/>
-      <c r="E105" s="16"/>
+      <c r="E105" s="15" t="s">
+        <v>36</v>
+      </c>
       <c r="F105" s="15" t="s">
         <v>23</v>
       </c>
       <c r="G105" s="16"/>
-      <c r="H105" s="16"/>
+      <c r="H105" s="15" t="s">
+        <v>144</v>
+      </c>
       <c r="I105" s="15" t="s">
-        <v>144</v>
+        <v>39</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="C106" s="15" t="s">
         <v>21</v>
@@ -3579,7 +3577,7 @@
       </c>
       <c r="G106" s="16"/>
       <c r="H106" s="15" t="s">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="I106" s="15" t="s">
         <v>39</v>
@@ -3587,10 +3585,10 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C107" s="15" t="s">
         <v>21</v>
@@ -3602,9 +3600,11 @@
       <c r="F107" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G107" s="16"/>
+      <c r="G107" s="15" t="s">
+        <v>111</v>
+      </c>
       <c r="H107" s="15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I107" s="15" t="s">
         <v>39</v>
@@ -3612,62 +3612,60 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="15" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="C108" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D108" s="16"/>
       <c r="E108" s="15" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F108" s="15" t="s">
         <v>23</v>
       </c>
       <c r="G108" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="H108" s="15" t="s">
-        <v>49</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="H108" s="16"/>
       <c r="I108" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="C109" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D109" s="16"/>
       <c r="E109" s="15" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F109" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G109" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H109" s="16"/>
+      <c r="G109" s="16"/>
+      <c r="H109" s="15" t="s">
+        <v>129</v>
+      </c>
       <c r="I109" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="C110" s="15" t="s">
         <v>21</v>
@@ -3681,7 +3679,7 @@
       </c>
       <c r="G110" s="16"/>
       <c r="H110" s="15" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="I110" s="15" t="s">
         <v>39</v>
@@ -3689,10 +3687,10 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="C111" s="15" t="s">
         <v>21</v>
@@ -3714,10 +3712,10 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C112" s="15" t="s">
         <v>21</v>
@@ -3729,9 +3727,11 @@
       <c r="F112" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G112" s="16"/>
+      <c r="G112" s="15" t="s">
+        <v>111</v>
+      </c>
       <c r="H112" s="15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I112" s="15" t="s">
         <v>39</v>
@@ -3739,85 +3739,81 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B113" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C113" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D113" s="16"/>
+      <c r="E113" s="16"/>
+      <c r="F113" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G113" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H113" s="16"/>
+      <c r="I113" s="15" t="s">
         <v>147</v>
-      </c>
-      <c r="B113" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C113" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D113" s="16"/>
-      <c r="E113" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F113" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="G113" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="H113" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="I113" s="15" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D114" s="16"/>
-      <c r="E114" s="16"/>
+      <c r="E114" s="15" t="s">
+        <v>22</v>
+      </c>
       <c r="F114" s="15" t="s">
         <v>23</v>
       </c>
       <c r="G114" s="15" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H114" s="16"/>
       <c r="I114" s="15" t="s">
-        <v>149</v>
+        <v>41</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D115" s="16"/>
-      <c r="E115" s="15" t="s">
-        <v>22</v>
-      </c>
+      <c r="E115" s="16"/>
       <c r="F115" s="15" t="s">
         <v>23</v>
       </c>
       <c r="G115" s="15" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H115" s="16"/>
       <c r="I115" s="15" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="C116" s="15" t="s">
         <v>27</v>
@@ -3828,42 +3824,44 @@
         <v>23</v>
       </c>
       <c r="G116" s="15" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H116" s="16"/>
       <c r="I116" s="15" t="s">
-        <v>97</v>
+        <v>150</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D117" s="16"/>
-      <c r="E117" s="16"/>
+      <c r="E117" s="15" t="s">
+        <v>36</v>
+      </c>
       <c r="F117" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G117" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="H117" s="16"/>
+      <c r="G117" s="16"/>
+      <c r="H117" s="15" t="s">
+        <v>46</v>
+      </c>
       <c r="I117" s="15" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C118" s="15" t="s">
         <v>21</v>
@@ -3875,9 +3873,11 @@
       <c r="F118" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G118" s="16"/>
+      <c r="G118" s="15" t="s">
+        <v>151</v>
+      </c>
       <c r="H118" s="15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I118" s="15" t="s">
         <v>39</v>
@@ -3885,10 +3885,10 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="C119" s="15" t="s">
         <v>21</v>
@@ -3900,11 +3900,9 @@
       <c r="F119" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G119" s="15" t="s">
-        <v>153</v>
-      </c>
+      <c r="G119" s="16"/>
       <c r="H119" s="15" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I119" s="15" t="s">
         <v>39</v>
@@ -3912,38 +3910,34 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="C120" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D120" s="16"/>
-      <c r="E120" s="15" t="s">
-        <v>36</v>
-      </c>
+      <c r="E120" s="16"/>
       <c r="F120" s="15" t="s">
         <v>23</v>
       </c>
       <c r="G120" s="16"/>
-      <c r="H120" s="15" t="s">
-        <v>46</v>
-      </c>
+      <c r="H120" s="16"/>
       <c r="I120" s="15" t="s">
-        <v>39</v>
+        <v>153</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B121" s="15" t="s">
         <v>154</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="D121" s="16"/>
       <c r="E121" s="16"/>
@@ -3953,53 +3947,33 @@
       <c r="G121" s="16"/>
       <c r="H121" s="16"/>
       <c r="I121" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="D122" s="16"/>
       <c r="E122" s="16"/>
       <c r="F122" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G122" s="16"/>
+      <c r="G122" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="H122" s="16"/>
       <c r="I122" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="B123" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C123" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D123" s="16"/>
-      <c r="E123" s="16"/>
-      <c r="F123" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="G123" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H123" s="16"/>
-      <c r="I123" s="15" t="s">
-        <v>159</v>
-      </c>
-    </row>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C10:C13" type="list">
@@ -4045,89 +4019,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4135,7 +4109,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>12</v>
@@ -4150,10 +4124,10 @@
         <v>15</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>18</v>
@@ -4161,16 +4135,16 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>184</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>186</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>22</v>
@@ -4179,160 +4153,160 @@
         <v>23</v>
       </c>
       <c r="G17" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="I17" s="14" t="s">
         <v>187</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="E18" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="F18" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>192</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="C19" s="12" t="s">
+      <c r="E19" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="F19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="H19" s="11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="H20" s="7" t="s">
         <v>197</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C21" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>191</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>193</v>
       </c>
       <c r="F21" s="13" t="s">
         <v>69</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="E22" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="I22" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>22</v>
@@ -4341,65 +4315,65 @@
         <v>23</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="C24" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="H24" s="7" t="s">
         <v>208</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B25" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="13" t="s">
+      <c r="H25" s="11" t="s">
         <v>212</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -4434,7 +4408,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>36</v>
@@ -4445,23 +4419,23 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4471,27 +4445,27 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
